--- a/checklist_forms/026_page_management_checklist--checklist_forms.xlsx
+++ b/checklist_forms/026_page_management_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>page_design</t>
+          <t>page design</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>page_layout</t>
+          <t>page layout</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>content_strategy</t>
+          <t>content strategy</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>page_testing</t>
+          <t>page testing</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>page_launch</t>
+          <t>page launch</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>content_review</t>
+          <t>content review</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>user_experience</t>
+          <t>user experience</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>technical_requirements</t>
+          <t>technical requirements</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>performance_requirements</t>
+          <t>performance requirements</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>security_requirements</t>
+          <t>security requirements</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>accessibility_requirements</t>
+          <t>accessibility requirements</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>search_engine_optimization</t>
+          <t>search engine optimization</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>content_management</t>
+          <t>content management</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>data_management</t>
+          <t>data management</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>analytics_reporting</t>
+          <t>analytics reporting</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>technical_support</t>
+          <t>technical support</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>content_updates</t>
+          <t>content updates</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>design_update</t>
+          <t>design update</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>content_update</t>
+          <t>content update</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>launch_update</t>
+          <t>launch update</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>review_update</t>
+          <t>review update</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>page_design</t>
+          <t>page design</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>page_layout</t>
+          <t>page layout</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>content_strategy</t>
+          <t>content strategy</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>page_testing</t>
+          <t>page testing</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>page_launch</t>
+          <t>page launch</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>content_review</t>
+          <t>content review</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>user_experience</t>
+          <t>user experience</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>technical_requirements</t>
+          <t>technical requirements</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>performance_requirements</t>
+          <t>performance requirements</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>security_requirements</t>
+          <t>security requirements</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>accessibility_requirements</t>
+          <t>accessibility requirements</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>search_engine_optimization</t>
+          <t>search engine optimization</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>content_management</t>
+          <t>content management</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>data_management</t>
+          <t>data management</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>analytics_reporting</t>
+          <t>analytics reporting</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>technical_support</t>
+          <t>technical support</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>content_updates</t>
+          <t>content updates</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>design_update</t>
+          <t>design update</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>content_update</t>
+          <t>content update</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>launch_update</t>
+          <t>launch update</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>review_update</t>
+          <t>review update</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>content_review_update</t>
+          <t>content review update</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>content_management_update</t>
+          <t>content management update</t>
         </is>
       </c>
     </row>
